--- a/sample-data/goc-ho-coffee/05_so_thu_chi_3_thang.xlsx
+++ b/sample-data/goc-ho-coffee/05_so_thu_chi_3_thang.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tóm tắt" sheetId="1" r:id="R796fbca127b541a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sổ thu chi" sheetId="2" r:id="Rca376671f2624d71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kiểm tra" sheetId="3" r:id="R90e2509fbbef46c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tóm tắt" sheetId="1" r:id="R8938cea2d3f240ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sổ thu chi" sheetId="2" r:id="R6212de1d49c94135"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kiểm tra" sheetId="3" r:id="Ra7c6c3614bba4c9c"/>
   </x:sheets>
 </x:workbook>
 </file>
